--- a/BSUIR/semestre 5/IAD/ИАД ПР.xlsx
+++ b/BSUIR/semestre 5/IAD/ИАД ПР.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="23001"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22527"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Goodvin\Documents\GitHub\study-repos\BSUIR\semestre 5\IAD\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\minsk\Documents\GitHub\study-repos\BSUIR\semestre 5\IAD\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75FB3E5A-FC2D-4D80-9C15-981D0F907239}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{454B0233-15FA-405C-B97E-49E1272B5AEE}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="12000" yWindow="945" windowWidth="14880" windowHeight="18450" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5115" yWindow="1035" windowWidth="15375" windowHeight="7875" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Задание 1" sheetId="1" r:id="rId1"/>
@@ -15701,7 +15701,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{86F3EFB3-6972-4806-8863-49B25B9B0C7C}">
-  <dimension ref="A1:E21"/>
+  <dimension ref="A1:E28"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="4" max="4" width="13.5703125" customWidth="1"/>
@@ -15810,6 +15810,10 @@
       <c r="D9" s="8" t="s">
         <v>33</v>
       </c>
+      <c r="E9">
+        <f>_xlfn.NORM.DIST(A2,$E$2,1,TRUE)</f>
+        <v>7.1428107352713589E-3</v>
+      </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10">
@@ -15818,6 +15822,10 @@
       <c r="B10">
         <v>200</v>
       </c>
+      <c r="E10">
+        <f t="shared" ref="E10:E37" si="0">_xlfn.NORM.DIST(A3,$E$2,1,TRUE)</f>
+        <v>0.99461385404593328</v>
+      </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11">
@@ -15826,6 +15834,10 @@
       <c r="B11">
         <v>130</v>
       </c>
+      <c r="E11">
+        <f t="shared" si="0"/>
+        <v>2.8029327681617391E-4</v>
+      </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12">
@@ -15834,6 +15846,10 @@
       <c r="B12">
         <v>140</v>
       </c>
+      <c r="E12">
+        <f t="shared" si="0"/>
+        <v>7.3529259609647943E-2</v>
+      </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13">
@@ -15842,6 +15858,10 @@
       <c r="B13">
         <v>265</v>
       </c>
+      <c r="E13">
+        <f t="shared" si="0"/>
+        <v>0.70884031321165264</v>
+      </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14">
@@ -15850,6 +15870,10 @@
       <c r="B14">
         <v>185</v>
       </c>
+      <c r="E14">
+        <f t="shared" si="0"/>
+        <v>4.2935144699718097E-6</v>
+      </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15">
@@ -15858,6 +15882,10 @@
       <c r="B15">
         <v>112</v>
       </c>
+      <c r="E15">
+        <f t="shared" si="0"/>
+        <v>2.5184910054460716E-8</v>
+      </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16">
@@ -15866,45 +15894,111 @@
       <c r="B16">
         <v>140</v>
       </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="E16">
+        <f t="shared" si="0"/>
+        <v>7.3529259609647943E-2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>71</v>
       </c>
       <c r="B17">
         <v>150</v>
       </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="E17">
+        <f t="shared" si="0"/>
+        <v>0.9999973177042204</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>74</v>
       </c>
       <c r="B18">
         <v>165</v>
       </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="E18">
+        <f t="shared" si="0"/>
+        <v>2.8029327681617391E-4</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>75</v>
       </c>
       <c r="B19">
         <v>185</v>
       </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="E19">
+        <f t="shared" si="0"/>
+        <v>0.70884031321165264</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>75</v>
       </c>
       <c r="B20">
         <v>210</v>
       </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="E20">
+        <f t="shared" si="0"/>
+        <v>0.99999999999997824</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>76</v>
       </c>
       <c r="B21">
         <v>220</v>
+      </c>
+      <c r="E21">
+        <f t="shared" si="0"/>
+        <v>0.99461385404593328</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E22">
+        <f t="shared" si="0"/>
+        <v>4.2935144699718097E-6</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E23">
+        <f t="shared" si="0"/>
+        <v>2.5184910054460716E-8</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E24">
+        <f>_xlfn.NORM.DIST(A17,$E$2,1,TRUE)</f>
+        <v>0.32635522028791897</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E25">
+        <f t="shared" si="0"/>
+        <v>0.99461385404593328</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E26">
+        <f>_xlfn.NORM.DIST(A19,$E$2,1,TRUE)</f>
+        <v>0.99980738442436434</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E27">
+        <f>_xlfn.NORM.DIST(A20,$E$2,1,TRUE)</f>
+        <v>0.99980738442436434</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E28">
+        <f>_xlfn.NORM.DIST(A21,$E$2,1,TRUE)</f>
+        <v>0.9999973177042204</v>
       </c>
     </row>
   </sheetData>

--- a/BSUIR/semestre 5/IAD/ИАД ПР.xlsx
+++ b/BSUIR/semestre 5/IAD/ИАД ПР.xlsx
@@ -5,17 +5,20 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\minsk\Documents\GitHub\study-repos\BSUIR\semestre 5\IAD\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\minsk\Documents\GitHub\study-repos\BSUIR\semestre 5\IAD\Rodevich's datasets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{454B0233-15FA-405C-B97E-49E1272B5AEE}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{300F685B-47FB-4D8B-B2AB-252F3E229213}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5115" yWindow="1035" windowWidth="15375" windowHeight="7875" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Задание 1" sheetId="1" r:id="rId1"/>
     <sheet name="Задание 2" sheetId="2" r:id="rId2"/>
   </sheets>
+  <externalReferences>
+    <externalReference r:id="rId3"/>
+  </externalReferences>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -35,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="45">
   <si>
     <t>1000 чисел</t>
   </si>
@@ -124,39 +127,64 @@
     <t>Y</t>
   </si>
   <si>
-    <t>Среднее X</t>
+    <t>Для X</t>
   </si>
   <si>
-    <t>Медиана X</t>
+    <t>Для Y</t>
   </si>
   <si>
-    <t>Мода X</t>
+    <t>Нормальное распределение Х</t>
   </si>
   <si>
-    <t>Дисперсия Y</t>
+    <t>Среднее:</t>
   </si>
   <si>
-    <t>Норм расп.</t>
+    <t>Дисперсия:</t>
+  </si>
+  <si>
+    <t>Медиана:</t>
+  </si>
+  <si>
+    <t>Вероятность &gt; 60:</t>
+  </si>
+  <si>
+    <t>Мода:</t>
+  </si>
+  <si>
+    <t>Коэффицент линейной уравнения регресии:</t>
+  </si>
+  <si>
+    <t>Уравнение имеет вид: Y = a*X + b.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Предсказанное значенее </t>
+  </si>
+  <si>
+    <t>Классификация</t>
+  </si>
+  <si>
+    <t>a=</t>
+  </si>
+  <si>
+    <t>b=</t>
+  </si>
+  <si>
+    <t>Порог=</t>
+  </si>
+  <si>
+    <t>Корреляция X-Y:</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="204"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -176,13 +204,6 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="13"/>
-      <color rgb="FF333333"/>
-      <name val="Arial"/>
-      <family val="2"/>
-      <charset val="204"/>
-    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -192,7 +213,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -222,16 +243,100 @@
     </border>
     <border>
       <left style="medium">
-        <color rgb="FFCECECE"/>
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
       </left>
       <right style="medium">
-        <color rgb="FFCECECE"/>
+        <color indexed="64"/>
       </right>
       <top style="medium">
-        <color rgb="FFCECECE"/>
+        <color indexed="64"/>
       </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
       <bottom style="medium">
-        <color rgb="FFCECECE"/>
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
@@ -239,23 +344,36 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -320,108 +438,106 @@
           </c:tx>
           <c:invertIfNegative val="0"/>
           <c:cat>
-            <c:strRef>
+            <c:numRef>
               <c:f>'Задание 1'!$O$3:$O$34</c:f>
-              <c:strCache>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
                 <c:ptCount val="32"/>
                 <c:pt idx="0">
-                  <c:v>-30,4170562</c:v>
+                  <c:v>-30.417056202888489</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>-28,0722263</c:v>
+                  <c:v>-28.072226301316292</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>-25,7273964</c:v>
+                  <c:v>-25.727396399744094</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>-23,3825665</c:v>
+                  <c:v>-23.382566498171897</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>-21,0377366</c:v>
+                  <c:v>-21.0377365965997</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>-18,6929067</c:v>
+                  <c:v>-18.692906695027503</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>-16,34807679</c:v>
+                  <c:v>-16.348076793455309</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>-14,00324689</c:v>
+                  <c:v>-14.003246891883112</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>-11,65841699</c:v>
+                  <c:v>-11.658416990310915</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>-9,313587089</c:v>
+                  <c:v>-9.3135870887387178</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>-6,968757187</c:v>
+                  <c:v>-6.9687571871665206</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>-4,623927286</c:v>
+                  <c:v>-4.6239272855943234</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>-2,279097384</c:v>
+                  <c:v>-2.2790973840221298</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0,065732518</c:v>
+                  <c:v>6.5732517550067371E-2</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>2,410562419</c:v>
+                  <c:v>2.4105624191222645</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>4,755392321</c:v>
+                  <c:v>4.7553923206944617</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>7,100222222</c:v>
+                  <c:v>7.1002222222666589</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>9,445052124</c:v>
+                  <c:v>9.4450521238388561</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>11,78988203</c:v>
+                  <c:v>11.789882025411053</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>14,13471193</c:v>
+                  <c:v>14.13471192698325</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>16,47954183</c:v>
+                  <c:v>16.479541828555448</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>18,82437173</c:v>
+                  <c:v>18.824371730127645</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>21,16920163</c:v>
+                  <c:v>21.169201631699842</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>23,51403153</c:v>
+                  <c:v>23.514031533272039</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>25,85886143</c:v>
+                  <c:v>25.858861434844229</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>28,20369134</c:v>
+                  <c:v>28.203691336416426</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>30,54852124</c:v>
+                  <c:v>30.548521237988624</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>32,89335114</c:v>
+                  <c:v>32.893351139560821</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>35,23818104</c:v>
+                  <c:v>35.238181041133018</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>37,58301094</c:v>
+                  <c:v>37.583010942705215</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>39,92784084</c:v>
-                </c:pt>
-                <c:pt idx="31">
-                  <c:v>Еще</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
+                  <c:v>39.927840844277412</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
@@ -521,9 +637,6 @@
                 </c:pt>
                 <c:pt idx="30">
                   <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="31">
-                  <c:v>1</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -691,81 +804,79 @@
           </c:tx>
           <c:invertIfNegative val="0"/>
           <c:cat>
-            <c:strRef>
+            <c:numRef>
               <c:f>'Задание 1'!$O$38:$O$60</c:f>
-              <c:strCache>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
                 <c:ptCount val="23"/>
                 <c:pt idx="0">
-                  <c:v>0,011443242</c:v>
+                  <c:v>1.1443242139648646E-2</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1,932408129</c:v>
+                  <c:v>1.9324081286719197</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>3,853373015</c:v>
+                  <c:v>3.8533730152041907</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>5,774337902</c:v>
+                  <c:v>5.7743379017364616</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>7,695302788</c:v>
+                  <c:v>7.6953027882687328</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>9,616267675</c:v>
+                  <c:v>9.6162676748010032</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>11,53723256</c:v>
+                  <c:v>11.537232561333274</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>13,45819745</c:v>
+                  <c:v>13.458197447865546</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>15,37916233</c:v>
+                  <c:v>15.379162334397817</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>17,30012722</c:v>
+                  <c:v>17.300127220930086</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>19,22109211</c:v>
+                  <c:v>19.221092107462358</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>21,14205699</c:v>
+                  <c:v>21.142056993994629</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>23,06302188</c:v>
+                  <c:v>23.0630218805269</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>24,98398677</c:v>
+                  <c:v>24.983986767059172</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>26,90495165</c:v>
+                  <c:v>26.904951653591443</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>28,82591654</c:v>
+                  <c:v>28.825916540123714</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>30,74688143</c:v>
+                  <c:v>30.746881426655985</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>32,66784631</c:v>
+                  <c:v>32.667846313188257</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>34,5888112</c:v>
+                  <c:v>34.588811199720524</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>36,50977609</c:v>
+                  <c:v>36.509776086252799</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>38,43074097</c:v>
+                  <c:v>38.430740972785067</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>40,35170586</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>Еще</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
+                  <c:v>40.351705859317342</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
@@ -838,9 +949,6 @@
                 </c:pt>
                 <c:pt idx="21">
                   <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>1</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1315,81 +1423,79 @@
           </c:tx>
           <c:invertIfNegative val="0"/>
           <c:cat>
-            <c:strRef>
+            <c:numRef>
               <c:f>'Задание 1'!$AZ$4:$AZ$26</c:f>
-              <c:strCache>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
                 <c:ptCount val="23"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0,045454545</c:v>
+                  <c:v>4.5454545454545456E-2</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0,090909091</c:v>
+                  <c:v>9.0909090909090912E-2</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0,136363636</c:v>
+                  <c:v>0.13636363636363635</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0,181818182</c:v>
+                  <c:v>0.18181818181818182</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0,227272727</c:v>
+                  <c:v>0.22727272727272729</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0,272727273</c:v>
+                  <c:v>0.27272727272727271</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0,318181818</c:v>
+                  <c:v>0.31818181818181818</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0,363636364</c:v>
+                  <c:v>0.36363636363636365</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0,409090909</c:v>
+                  <c:v>0.40909090909090912</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0,454545455</c:v>
+                  <c:v>0.45454545454545459</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0,5</c:v>
+                  <c:v>0.5</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0,545454545</c:v>
+                  <c:v>0.54545454545454541</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0,590909091</c:v>
+                  <c:v>0.59090909090909094</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>0,636363636</c:v>
+                  <c:v>0.63636363636363635</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>0,681818182</c:v>
+                  <c:v>0.68181818181818188</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>0,727272727</c:v>
+                  <c:v>0.72727272727272729</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>0,772727273</c:v>
+                  <c:v>0.77272727272727271</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>0,818181818</c:v>
+                  <c:v>0.81818181818181823</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>0,863636364</c:v>
+                  <c:v>0.86363636363636365</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>0,909090909</c:v>
+                  <c:v>0.90909090909090917</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>0,954545455</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>Еще</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
+                  <c:v>0.95454545454545459</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
@@ -1462,9 +1568,6 @@
                 </c:pt>
                 <c:pt idx="21">
                   <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>1</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1580,18 +1683,3048 @@
 </c:chartSpace>
 </file>
 
+<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="ru-RU"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="ru-RU"/>
+              <a:t>Нормальное</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="ru-RU" baseline="0"/>
+              <a:t> распределение для </a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" baseline="0"/>
+              <a:t>X</a:t>
+            </a:r>
+            <a:endParaRPr lang="ru-RU"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="ru-RU"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>'Задание 2'!$H$2:$H$21</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="20"/>
+                <c:pt idx="0">
+                  <c:v>0.26052911964344094</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.7479036683721495</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.18309329220754714</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.35205046066158219</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.5572728515956753</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.12189538425686426</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>7.6719568903845278E-2</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.35205046066158219</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.88332162244271784</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.18309329220754714</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.5572728515956753</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.97600912012813501</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0.7479036683721495</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0.12189538425686426</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>7.6719568903845278E-2</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>0.45308690767740317</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>0.7479036683721495</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>0.82377095162645231</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>0.82377095162645231</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>0.88332162244271784</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Задание 2'!$A$2:$A$21</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="20"/>
+                <c:pt idx="0">
+                  <c:v>69</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>74</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>68</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>70</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>72</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>67</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>66</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>70</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>76</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>68</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>72</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>79</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>74</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>67</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>66</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>71</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>74</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>75</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>75</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>76</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-AE2A-4E7B-AFB6-86524B32AC4F}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:smooth val="0"/>
+        <c:axId val="1341440527"/>
+        <c:axId val="1341438127"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="1341440527"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ru-RU"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1341438127"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1341438127"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ru-RU"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1341440527"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="ru-RU"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="ru-RU"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="ru-RU"/>
+              <a:t>Гистограмма</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="ru-RU" baseline="0"/>
+              <a:t> </a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" baseline="0"/>
+              <a:t>X </a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="ru-RU" baseline="0"/>
+              <a:t>и </a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" baseline="0"/>
+              <a:t>Y</a:t>
+            </a:r>
+            <a:endParaRPr lang="ru-RU"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="ru-RU"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Задание 2'!$A$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>X</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:val>
+            <c:numRef>
+              <c:f>'Задание 2'!$A$2:$A$21</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="20"/>
+                <c:pt idx="0">
+                  <c:v>69</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>74</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>68</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>70</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>72</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>67</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>66</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>70</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>76</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>68</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>72</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>79</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>74</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>67</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>66</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>71</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>74</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>75</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>75</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>76</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-8F48-4327-B797-31B2DB1D2E0D}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Задание 2'!$B$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Y</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent2"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:val>
+            <c:numRef>
+              <c:f>'Задание 2'!$B$2:$B$21</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="20"/>
+                <c:pt idx="0">
+                  <c:v>153</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>175</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>155</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>135</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>172</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>150</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>115</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>137</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>200</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>130</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>140</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>265</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>185</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>112</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>140</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>150</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>165</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>185</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>210</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>220</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-8F48-4327-B797-31B2DB1D2E0D}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="219"/>
+        <c:overlap val="-27"/>
+        <c:axId val="1586587231"/>
+        <c:axId val="1586586271"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="1586587231"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ru-RU"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1586586271"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1586586271"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ru-RU"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1586587231"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="ru-RU"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="ru-RU"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart7.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="ru-RU"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="ru-RU"/>
+              <a:t>Диаграмма рассеяния</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="ru-RU"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:v>Х</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="25400" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'Задание 2'!$A$2:$A$21</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="20"/>
+                <c:pt idx="0">
+                  <c:v>69</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>74</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>68</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>70</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>72</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>67</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>66</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>70</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>76</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>68</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>72</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>79</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>74</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>67</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>66</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>71</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>74</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>75</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>75</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>76</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-7473-4D8A-8993-5352DC4EEC11}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:v>Y</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="25400" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent2"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'Задание 2'!$B$2:$B$21</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="20"/>
+                <c:pt idx="0">
+                  <c:v>153</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>175</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>155</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>135</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>172</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>150</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>115</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>137</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>200</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>130</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>140</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>265</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>185</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>112</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>140</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>150</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>165</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>185</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>210</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>220</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-7473-4D8A-8993-5352DC4EEC11}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="1838605535"/>
+        <c:axId val="1838604575"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="1838605535"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ru-RU"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1838604575"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="1838604575"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ru-RU"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1838605535"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="ru-RU"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="ru-RU"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>22</xdr:col>
-      <xdr:colOff>257175</xdr:colOff>
+      <xdr:colOff>219075</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>190500</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>28</xdr:col>
-      <xdr:colOff>372001</xdr:colOff>
+      <xdr:colOff>333901</xdr:colOff>
       <xdr:row>18</xdr:row>
       <xdr:rowOff>170248</xdr:rowOff>
     </xdr:to>
@@ -1616,8 +4749,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="16259175" y="190500"/>
-          <a:ext cx="3772426" cy="3429479"/>
+          <a:off x="16221075" y="190500"/>
+          <a:ext cx="3772426" cy="3427798"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1859,6 +4992,369 @@
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>95249</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>100012</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>495300</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>180975</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Диаграмма 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C47FAEA4-CEAF-48D1-B704-74C4E14764D4}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>104774</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>23812</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>485774</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>57150</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Диаграмма 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4F162DA0-C2D5-4F55-BE9B-33B910D5DD38}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>285750</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>100012</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>600075</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>176212</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="4" name="Диаграмма 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D4D67EB0-7CA0-42AA-81D2-91605EF0DA3D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="Задание 1"/>
+      <sheetName val="Задание 2"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1">
+        <row r="1">
+          <cell r="A1" t="str">
+            <v>X</v>
+          </cell>
+          <cell r="B1" t="str">
+            <v>Y</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="A2">
+            <v>69</v>
+          </cell>
+          <cell r="B2">
+            <v>153</v>
+          </cell>
+          <cell r="H2">
+            <v>0.26052911964344094</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="A3">
+            <v>74</v>
+          </cell>
+          <cell r="B3">
+            <v>175</v>
+          </cell>
+          <cell r="H3">
+            <v>0.7479036683721495</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="A4">
+            <v>68</v>
+          </cell>
+          <cell r="B4">
+            <v>155</v>
+          </cell>
+          <cell r="H4">
+            <v>0.18309329220754714</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="A5">
+            <v>70</v>
+          </cell>
+          <cell r="B5">
+            <v>135</v>
+          </cell>
+          <cell r="H5">
+            <v>0.35205046066158219</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="A6">
+            <v>72</v>
+          </cell>
+          <cell r="B6">
+            <v>172</v>
+          </cell>
+          <cell r="H6">
+            <v>0.5572728515956753</v>
+          </cell>
+        </row>
+        <row r="7">
+          <cell r="A7">
+            <v>67</v>
+          </cell>
+          <cell r="B7">
+            <v>150</v>
+          </cell>
+          <cell r="H7">
+            <v>0.12189538425686426</v>
+          </cell>
+        </row>
+        <row r="8">
+          <cell r="A8">
+            <v>66</v>
+          </cell>
+          <cell r="B8">
+            <v>115</v>
+          </cell>
+          <cell r="H8">
+            <v>7.6719568903845278E-2</v>
+          </cell>
+        </row>
+        <row r="9">
+          <cell r="A9">
+            <v>70</v>
+          </cell>
+          <cell r="B9">
+            <v>137</v>
+          </cell>
+          <cell r="H9">
+            <v>0.35205046066158219</v>
+          </cell>
+        </row>
+        <row r="10">
+          <cell r="A10">
+            <v>76</v>
+          </cell>
+          <cell r="B10">
+            <v>200</v>
+          </cell>
+          <cell r="H10">
+            <v>0.88332162244271784</v>
+          </cell>
+        </row>
+        <row r="11">
+          <cell r="A11">
+            <v>68</v>
+          </cell>
+          <cell r="B11">
+            <v>130</v>
+          </cell>
+          <cell r="H11">
+            <v>0.18309329220754714</v>
+          </cell>
+        </row>
+        <row r="12">
+          <cell r="A12">
+            <v>72</v>
+          </cell>
+          <cell r="B12">
+            <v>140</v>
+          </cell>
+          <cell r="H12">
+            <v>0.5572728515956753</v>
+          </cell>
+        </row>
+        <row r="13">
+          <cell r="A13">
+            <v>79</v>
+          </cell>
+          <cell r="B13">
+            <v>265</v>
+          </cell>
+          <cell r="H13">
+            <v>0.97600912012813501</v>
+          </cell>
+        </row>
+        <row r="14">
+          <cell r="A14">
+            <v>74</v>
+          </cell>
+          <cell r="B14">
+            <v>185</v>
+          </cell>
+          <cell r="H14">
+            <v>0.7479036683721495</v>
+          </cell>
+        </row>
+        <row r="15">
+          <cell r="A15">
+            <v>67</v>
+          </cell>
+          <cell r="B15">
+            <v>112</v>
+          </cell>
+          <cell r="H15">
+            <v>0.12189538425686426</v>
+          </cell>
+        </row>
+        <row r="16">
+          <cell r="A16">
+            <v>66</v>
+          </cell>
+          <cell r="B16">
+            <v>140</v>
+          </cell>
+          <cell r="H16">
+            <v>7.6719568903845278E-2</v>
+          </cell>
+        </row>
+        <row r="17">
+          <cell r="A17">
+            <v>71</v>
+          </cell>
+          <cell r="B17">
+            <v>150</v>
+          </cell>
+          <cell r="H17">
+            <v>0.45308690767740317</v>
+          </cell>
+        </row>
+        <row r="18">
+          <cell r="A18">
+            <v>74</v>
+          </cell>
+          <cell r="B18">
+            <v>165</v>
+          </cell>
+          <cell r="H18">
+            <v>0.7479036683721495</v>
+          </cell>
+        </row>
+        <row r="19">
+          <cell r="A19">
+            <v>75</v>
+          </cell>
+          <cell r="B19">
+            <v>185</v>
+          </cell>
+          <cell r="H19">
+            <v>0.82377095162645231</v>
+          </cell>
+        </row>
+        <row r="20">
+          <cell r="A20">
+            <v>75</v>
+          </cell>
+          <cell r="B20">
+            <v>210</v>
+          </cell>
+          <cell r="H20">
+            <v>0.82377095162645231</v>
+          </cell>
+        </row>
+        <row r="21">
+          <cell r="A21">
+            <v>76</v>
+          </cell>
+          <cell r="B21">
+            <v>220</v>
+          </cell>
+          <cell r="H21">
+            <v>0.88332162244271784</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2131,6 +5627,10 @@
     <col min="12" max="12" width="28.42578125" customWidth="1"/>
     <col min="35" max="35" width="26.85546875" customWidth="1"/>
     <col min="36" max="36" width="15" customWidth="1"/>
+    <col min="44" max="44" width="15.5703125" customWidth="1"/>
+    <col min="49" max="49" width="27.28515625" bestFit="1" customWidth="1"/>
+    <col min="50" max="50" width="12" bestFit="1" customWidth="1"/>
+    <col min="52" max="52" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:66" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -3362,12 +6862,8 @@
         <f t="shared" si="1"/>
         <v>0.33214154075263908</v>
       </c>
-      <c r="AZ26" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="BA26" s="3">
-        <v>1</v>
-      </c>
+      <c r="AZ26" s="3"/>
+      <c r="BA26" s="3"/>
     </row>
     <row r="27" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A27">
@@ -3604,12 +7100,8 @@
         <f t="shared" si="0"/>
         <v>11.488594302325509</v>
       </c>
-      <c r="O34" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="P34" s="3">
-        <v>1</v>
-      </c>
+      <c r="O34" s="3"/>
+      <c r="P34" s="3"/>
       <c r="AE34">
         <f t="shared" si="2"/>
         <v>0.25573274472710039</v>
@@ -4358,12 +7850,8 @@
         <f t="shared" si="0"/>
         <v>9.9893832359230146</v>
       </c>
-      <c r="O60" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="P60" s="3">
-        <v>1</v>
-      </c>
+      <c r="O60" s="3"/>
+      <c r="P60" s="3"/>
       <c r="AE60">
         <f t="shared" si="2"/>
         <v>5.0112921409793773E-2</v>
@@ -15695,315 +19183,567 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{86F3EFB3-6972-4806-8863-49B25B9B0C7C}">
-  <dimension ref="A1:E28"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D2DDADC1-BAE6-4B85-ADA6-0800BE8E08FF}">
+  <dimension ref="A1:J48"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="4" max="4" width="13.5703125" customWidth="1"/>
+    <col min="3" max="3" width="11.5703125" customWidth="1"/>
+    <col min="5" max="5" width="41.7109375" customWidth="1"/>
+    <col min="8" max="8" width="35" customWidth="1"/>
+    <col min="9" max="9" width="23.85546875" customWidth="1"/>
+    <col min="10" max="10" width="16.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="8" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2">
+      <c r="C1" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1" s="16"/>
+      <c r="E1" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="F1" s="16"/>
+      <c r="H1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="9">
         <v>69</v>
       </c>
-      <c r="B2">
+      <c r="B2" s="10">
         <v>153</v>
       </c>
-      <c r="D2" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="E2" s="7">
+      <c r="C2" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="D2" s="11">
         <f>AVERAGE(A2:A21)</f>
         <v>71.45</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3">
+      <c r="E2" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="F2" s="13">
+        <f>_xlfn.VAR.S(B2:B21)</f>
+        <v>1441.2736842105239</v>
+      </c>
+      <c r="H2">
+        <f>_xlfn.NORM.DIST(A2, $D$2, _xlfn.STDEV.S($A$2:$A$21), TRUE)</f>
+        <v>0.26052911964344094</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" s="9">
         <v>74</v>
       </c>
-      <c r="B3">
+      <c r="B3" s="10">
         <v>175</v>
       </c>
-      <c r="D3" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="E3" s="7">
+      <c r="C3" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="D3" s="11">
         <f>MEDIAN(A2:A21)</f>
         <v>71.5</v>
       </c>
-    </row>
-    <row r="4" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4">
+      <c r="E3" t="s">
+        <v>35</v>
+      </c>
+      <c r="F3">
+        <f>COUNTIF(A2:A21, "&gt;" &amp; 60) / 20</f>
+        <v>1</v>
+      </c>
+      <c r="H3">
+        <f t="shared" ref="H3:H21" si="0">_xlfn.NORM.DIST(A3, $D$2, _xlfn.STDEV.S($A$2:$A$21), TRUE)</f>
+        <v>0.7479036683721495</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="9">
         <v>68</v>
       </c>
-      <c r="B4">
+      <c r="B4" s="10">
         <v>155</v>
       </c>
-      <c r="D4" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="E4" s="7">
-        <f>MODE(A2:A21)</f>
+      <c r="C4" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="D4" s="13">
+        <f>_xlfn.MODE.SNGL(A2:A21)</f>
         <v>74</v>
       </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5">
+      <c r="E4" t="s">
+        <v>44</v>
+      </c>
+      <c r="F4">
+        <f>CORREL(A2:A21, B2:B21)</f>
+        <v>0.88917013517480481</v>
+      </c>
+      <c r="H4">
+        <f t="shared" si="0"/>
+        <v>0.18309329220754714</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" s="9">
         <v>70</v>
       </c>
-      <c r="B5">
+      <c r="B5" s="10">
         <v>135</v>
       </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6">
+      <c r="E5" t="s">
+        <v>37</v>
+      </c>
+      <c r="F5">
+        <f>LINEST(B2:B21,A2:A21,TRUE,TRUE)</f>
+        <v>8.841668171150026</v>
+      </c>
+      <c r="H5">
+        <f t="shared" si="0"/>
+        <v>0.35205046066158219</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" s="9">
         <v>72</v>
       </c>
-      <c r="B6">
+      <c r="B6" s="10">
         <v>172</v>
       </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7">
+      <c r="H6">
+        <f t="shared" si="0"/>
+        <v>0.5572728515956753</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" s="9">
         <v>67</v>
       </c>
-      <c r="B7">
+      <c r="B7" s="10">
         <v>150</v>
       </c>
-      <c r="D7" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="E7">
-        <f>VAR(B2:B21)</f>
-        <v>1441.2736842105239</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8">
+      <c r="H7">
+        <f t="shared" si="0"/>
+        <v>0.12189538425686426</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" s="9">
         <v>66</v>
       </c>
-      <c r="B8">
+      <c r="B8" s="10">
         <v>115</v>
       </c>
-      <c r="D8" s="9"/>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9">
+      <c r="H8">
+        <f t="shared" si="0"/>
+        <v>7.6719568903845278E-2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" s="9">
         <v>70</v>
       </c>
-      <c r="B9">
+      <c r="B9" s="10">
         <v>137</v>
       </c>
-      <c r="D9" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="E9">
-        <f>_xlfn.NORM.DIST(A2,$E$2,1,TRUE)</f>
-        <v>7.1428107352713589E-3</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10">
+      <c r="H9">
+        <f t="shared" si="0"/>
+        <v>0.35205046066158219</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" s="9">
         <v>76</v>
       </c>
-      <c r="B10">
+      <c r="B10" s="10">
         <v>200</v>
       </c>
-      <c r="E10">
-        <f t="shared" ref="E10:E37" si="0">_xlfn.NORM.DIST(A3,$E$2,1,TRUE)</f>
-        <v>0.99461385404593328</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11">
+      <c r="H10">
+        <f t="shared" si="0"/>
+        <v>0.88332162244271784</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" s="9">
         <v>68</v>
       </c>
-      <c r="B11">
+      <c r="B11" s="10">
         <v>130</v>
       </c>
-      <c r="E11">
+      <c r="H11">
         <f t="shared" si="0"/>
-        <v>2.8029327681617391E-4</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A12">
+        <v>0.18309329220754714</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" s="9">
         <v>72</v>
       </c>
-      <c r="B12">
+      <c r="B12" s="10">
         <v>140</v>
       </c>
-      <c r="E12">
+      <c r="H12">
         <f t="shared" si="0"/>
-        <v>7.3529259609647943E-2</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A13">
+        <v>0.5572728515956753</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" s="9">
         <v>79</v>
       </c>
-      <c r="B13">
+      <c r="B13" s="10">
         <v>265</v>
       </c>
-      <c r="E13">
+      <c r="H13">
         <f t="shared" si="0"/>
-        <v>0.70884031321165264</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A14">
+        <v>0.97600912012813501</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" s="9">
         <v>74</v>
       </c>
-      <c r="B14">
+      <c r="B14" s="10">
         <v>185</v>
       </c>
-      <c r="E14">
+      <c r="H14">
         <f t="shared" si="0"/>
-        <v>4.2935144699718097E-6</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A15">
+        <v>0.7479036683721495</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" s="9">
         <v>67</v>
       </c>
-      <c r="B15">
+      <c r="B15" s="10">
         <v>112</v>
       </c>
-      <c r="E15">
+      <c r="H15">
         <f t="shared" si="0"/>
-        <v>2.5184910054460716E-8</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A16">
+        <v>0.12189538425686426</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" s="9">
         <v>66</v>
       </c>
-      <c r="B16">
+      <c r="B16" s="10">
         <v>140</v>
       </c>
-      <c r="E16">
+      <c r="H16">
         <f t="shared" si="0"/>
-        <v>7.3529259609647943E-2</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A17">
+        <v>7.6719568903845278E-2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A17" s="9">
         <v>71</v>
       </c>
-      <c r="B17">
+      <c r="B17" s="10">
         <v>150</v>
       </c>
-      <c r="E17">
+      <c r="H17">
         <f t="shared" si="0"/>
-        <v>0.9999973177042204</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A18">
+        <v>0.45308690767740317</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A18" s="9">
         <v>74</v>
       </c>
-      <c r="B18">
+      <c r="B18" s="10">
         <v>165</v>
       </c>
-      <c r="E18">
+      <c r="H18">
         <f t="shared" si="0"/>
-        <v>2.8029327681617391E-4</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A19">
+        <v>0.7479036683721495</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A19" s="9">
         <v>75</v>
       </c>
-      <c r="B19">
+      <c r="B19" s="10">
         <v>185</v>
       </c>
-      <c r="E19">
+      <c r="H19">
         <f t="shared" si="0"/>
-        <v>0.70884031321165264</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A20">
+        <v>0.82377095162645231</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A20" s="9">
         <v>75</v>
       </c>
-      <c r="B20">
+      <c r="B20" s="10">
         <v>210</v>
       </c>
-      <c r="E20">
+      <c r="H20">
         <f t="shared" si="0"/>
-        <v>0.99999999999997824</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A21">
+        <v>0.82377095162645231</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="12">
         <v>76</v>
       </c>
-      <c r="B21">
+      <c r="B21" s="14">
         <v>220</v>
       </c>
-      <c r="E21">
+      <c r="H21">
         <f t="shared" si="0"/>
-        <v>0.99461385404593328</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="E22">
-        <f t="shared" si="0"/>
-        <v>4.2935144699718097E-6</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="E23">
-        <f t="shared" si="0"/>
-        <v>2.5184910054460716E-8</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="E24">
-        <f>_xlfn.NORM.DIST(A17,$E$2,1,TRUE)</f>
-        <v>0.32635522028791897</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="E25">
-        <f t="shared" si="0"/>
-        <v>0.99461385404593328</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="E26">
-        <f>_xlfn.NORM.DIST(A19,$E$2,1,TRUE)</f>
-        <v>0.99980738442436434</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="E27">
-        <f>_xlfn.NORM.DIST(A20,$E$2,1,TRUE)</f>
-        <v>0.99980738442436434</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="E28">
-        <f>_xlfn.NORM.DIST(A21,$E$2,1,TRUE)</f>
-        <v>0.9999973177042204</v>
+        <v>0.88332162244271784</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="H28" t="s">
+        <v>38</v>
+      </c>
+      <c r="I28" t="s">
+        <v>39</v>
+      </c>
+      <c r="J28" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="G29" t="s">
+        <v>41</v>
+      </c>
+      <c r="H29">
+        <v>2</v>
+      </c>
+      <c r="I29">
+        <f xml:space="preserve"> $H$29 * A2 + $H$30</f>
+        <v>188</v>
+      </c>
+      <c r="J29">
+        <f>IF(I29 &gt; $H$31, 1, 0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="G30" t="s">
+        <v>42</v>
+      </c>
+      <c r="H30">
+        <v>50</v>
+      </c>
+      <c r="I30">
+        <f t="shared" ref="I30:I39" si="1" xml:space="preserve"> $H$29 * A3 + $H$30</f>
+        <v>198</v>
+      </c>
+      <c r="J30">
+        <f t="shared" ref="J30:J48" si="2">IF(I30 &gt; $H$31, 1, 0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="G31" t="s">
+        <v>43</v>
+      </c>
+      <c r="H31">
+        <v>190</v>
+      </c>
+      <c r="I31">
+        <f t="shared" si="1"/>
+        <v>186</v>
+      </c>
+      <c r="J31">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="I32">
+        <f t="shared" si="1"/>
+        <v>190</v>
+      </c>
+      <c r="J32">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I33">
+        <f t="shared" si="1"/>
+        <v>194</v>
+      </c>
+      <c r="J33">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I34">
+        <f t="shared" si="1"/>
+        <v>184</v>
+      </c>
+      <c r="J34">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I35">
+        <f t="shared" si="1"/>
+        <v>182</v>
+      </c>
+      <c r="J35">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I36">
+        <f t="shared" si="1"/>
+        <v>190</v>
+      </c>
+      <c r="J36">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I37">
+        <f t="shared" si="1"/>
+        <v>202</v>
+      </c>
+      <c r="J37">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I38">
+        <f t="shared" si="1"/>
+        <v>186</v>
+      </c>
+      <c r="J38">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I39">
+        <f t="shared" si="1"/>
+        <v>194</v>
+      </c>
+      <c r="J39">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I40">
+        <f xml:space="preserve"> $H$29 * A13 + $H$30</f>
+        <v>208</v>
+      </c>
+      <c r="J40">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I41">
+        <f t="shared" ref="I41:I48" si="3" xml:space="preserve"> $H$29 * A14 + $H$30</f>
+        <v>198</v>
+      </c>
+      <c r="J41">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I42">
+        <f t="shared" si="3"/>
+        <v>184</v>
+      </c>
+      <c r="J42">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I43">
+        <f t="shared" si="3"/>
+        <v>182</v>
+      </c>
+      <c r="J43">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I44">
+        <f t="shared" si="3"/>
+        <v>192</v>
+      </c>
+      <c r="J44">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I45">
+        <f t="shared" si="3"/>
+        <v>198</v>
+      </c>
+      <c r="J45">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I46">
+        <f t="shared" si="3"/>
+        <v>200</v>
+      </c>
+      <c r="J46">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I47">
+        <f t="shared" si="3"/>
+        <v>200</v>
+      </c>
+      <c r="J47">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I48">
+        <f t="shared" si="3"/>
+        <v>202</v>
+      </c>
+      <c r="J48">
+        <f t="shared" si="2"/>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="E1:F1"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
